--- a/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -2069,7 +2069,9 @@
       <c r="HO2" t="n">
         <v>50.627</v>
       </c>
-      <c r="HP2" t="inlineStr"/>
+      <c r="HP2" t="n">
+        <v>39.851</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2751,7 +2753,9 @@
       <c r="HO3" t="n">
         <v>1992.578</v>
       </c>
-      <c r="HP3" t="inlineStr"/>
+      <c r="HP3" t="n">
+        <v>1568.437</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3145,7 +3149,9 @@
       <c r="HO4" t="n">
         <v>1.318</v>
       </c>
-      <c r="HP4" t="inlineStr"/>
+      <c r="HP4" t="n">
+        <v>1.295</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3539,7 +3545,9 @@
       <c r="HO5" t="n">
         <v>51.888</v>
       </c>
-      <c r="HP5" t="inlineStr"/>
+      <c r="HP5" t="n">
+        <v>50.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4077,7 +4085,9 @@
       <c r="HO6" t="n">
         <v>980.452</v>
       </c>
-      <c r="HP6" t="inlineStr"/>
+      <c r="HP6" t="n">
+        <v>660.534</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4759,7 +4769,9 @@
       <c r="HO7" t="n">
         <v>38588.366</v>
       </c>
-      <c r="HP7" t="inlineStr"/>
+      <c r="HP7" t="n">
+        <v>25997.119</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5297,7 +5309,9 @@
       <c r="HO8" t="n">
         <v>1508.473</v>
       </c>
-      <c r="HP8" t="inlineStr"/>
+      <c r="HP8" t="n">
+        <v>736.1369999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5979,7 +5993,9 @@
       <c r="HO9" t="n">
         <v>59370.022</v>
       </c>
-      <c r="HP9" t="inlineStr"/>
+      <c r="HP9" t="n">
+        <v>28972.726</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6293,7 +6309,9 @@
       <c r="HO10" t="n">
         <v>-10.692</v>
       </c>
-      <c r="HP10" t="inlineStr"/>
+      <c r="HP10" t="n">
+        <v>-90.262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6607,7 +6625,9 @@
       <c r="HO11" t="n">
         <v>0</v>
       </c>
-      <c r="HP11" t="inlineStr"/>
+      <c r="HP11" t="n">
+        <v>-3552.48</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7145,7 +7165,9 @@
       <c r="HO12" t="n">
         <v>-1697.451</v>
       </c>
-      <c r="HP12" t="inlineStr"/>
+      <c r="HP12" t="n">
+        <v>-859.0700000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7827,7 +7849,9 @@
       <c r="HO13" t="n">
         <v>-66325.55899999999</v>
       </c>
-      <c r="HP13" t="inlineStr"/>
+      <c r="HP13" t="n">
+        <v>-33811.045</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8197,7 +8221,9 @@
       <c r="HO14" t="n">
         <v>0</v>
       </c>
-      <c r="HP14" t="inlineStr"/>
+      <c r="HP14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8567,7 +8593,9 @@
       <c r="HO15" t="n">
         <v>0</v>
       </c>
-      <c r="HP15" t="inlineStr"/>
+      <c r="HP15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9105,7 +9133,9 @@
       <c r="HO16" t="n">
         <v>1217.219</v>
       </c>
-      <c r="HP16" t="inlineStr"/>
+      <c r="HP16" t="n">
+        <v>908.323</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9667,7 +9697,9 @@
       <c r="HO17" t="n">
         <v>47906.958</v>
       </c>
-      <c r="HP17" t="inlineStr"/>
+      <c r="HP17" t="n">
+        <v>35749.511</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10205,7 +10237,9 @@
       <c r="HO18" t="n">
         <v>1232.067</v>
       </c>
-      <c r="HP18" t="inlineStr"/>
+      <c r="HP18" t="n">
+        <v>914.875</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10887,7 +10921,9 @@
       <c r="HO19" t="n">
         <v>47588.369</v>
       </c>
-      <c r="HP19" t="inlineStr"/>
+      <c r="HP19" t="n">
+        <v>36007.305</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11425,7 +11461,9 @@
       <c r="HO20" t="n">
         <v>392.023</v>
       </c>
-      <c r="HP20" t="inlineStr"/>
+      <c r="HP20" t="n">
+        <v>299.131</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12035,7 +12073,9 @@
       <c r="HO21" t="n">
         <v>15429.121</v>
       </c>
-      <c r="HP21" t="inlineStr"/>
+      <c r="HP21" t="n">
+        <v>11773.106</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12573,7 +12613,9 @@
       <c r="HO22" t="n">
         <v>11.644</v>
       </c>
-      <c r="HP22" t="inlineStr"/>
+      <c r="HP22" t="n">
+        <v>10.556</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13255,7 +13297,9 @@
       <c r="HO23" t="n">
         <v>458.283</v>
       </c>
-      <c r="HP23" t="inlineStr"/>
+      <c r="HP23" t="n">
+        <v>415.473</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13625,7 +13669,9 @@
       <c r="HO24" t="n">
         <v>0</v>
       </c>
-      <c r="HP24" t="inlineStr"/>
+      <c r="HP24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -13995,7 +14041,9 @@
       <c r="HO25" t="n">
         <v>0</v>
       </c>
-      <c r="HP25" t="inlineStr"/>
+      <c r="HP25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14365,7 +14413,9 @@
       <c r="HO26" t="n">
         <v>0</v>
       </c>
-      <c r="HP26" t="inlineStr"/>
+      <c r="HP26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14735,7 +14785,9 @@
       <c r="HO27" t="n">
         <v>0</v>
       </c>
-      <c r="HP27" t="inlineStr"/>
+      <c r="HP27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15543,7 +15595,9 @@
       <c r="HO30" t="n">
         <v>360.86</v>
       </c>
-      <c r="HP30" t="inlineStr"/>
+      <c r="HP30" t="n">
+        <v>247.462</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15851,7 +15905,9 @@
       <c r="HO31" t="n">
         <v>14202.609</v>
       </c>
-      <c r="HP31" t="inlineStr"/>
+      <c r="HP31" t="n">
+        <v>9739.558000000001</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16245,7 +16301,9 @@
       <c r="HO32" t="n">
         <v>14.848</v>
       </c>
-      <c r="HP32" t="inlineStr"/>
+      <c r="HP32" t="n">
+        <v>6.552</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16639,7 +16697,9 @@
       <c r="HO33" t="n">
         <v>-318.589</v>
       </c>
-      <c r="HP33" t="inlineStr"/>
+      <c r="HP33" t="n">
+        <v>257.794</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HP33"/>
+  <dimension ref="A1:HQ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,6 +1530,11 @@
       <c r="HP1" t="inlineStr">
         <is>
           <t>2026-02</t>
+        </is>
+      </c>
+      <c r="HQ1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -2072,6 +2077,7 @@
       <c r="HP2" t="n">
         <v>39.851</v>
       </c>
+      <c r="HQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2756,6 +2762,7 @@
       <c r="HP3" t="n">
         <v>1568.437</v>
       </c>
+      <c r="HQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3152,6 +3159,7 @@
       <c r="HP4" t="n">
         <v>1.295</v>
       </c>
+      <c r="HQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3548,6 +3556,7 @@
       <c r="HP5" t="n">
         <v>50.95</v>
       </c>
+      <c r="HQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4088,6 +4097,7 @@
       <c r="HP6" t="n">
         <v>660.534</v>
       </c>
+      <c r="HQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4772,6 +4782,7 @@
       <c r="HP7" t="n">
         <v>25997.119</v>
       </c>
+      <c r="HQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5312,6 +5323,7 @@
       <c r="HP8" t="n">
         <v>736.1369999999999</v>
       </c>
+      <c r="HQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5996,6 +6008,7 @@
       <c r="HP9" t="n">
         <v>28972.726</v>
       </c>
+      <c r="HQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6312,6 +6325,7 @@
       <c r="HP10" t="n">
         <v>-90.262</v>
       </c>
+      <c r="HQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6628,6 +6642,7 @@
       <c r="HP11" t="n">
         <v>-3552.48</v>
       </c>
+      <c r="HQ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7168,6 +7183,7 @@
       <c r="HP12" t="n">
         <v>-859.0700000000001</v>
       </c>
+      <c r="HQ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7852,6 +7868,7 @@
       <c r="HP13" t="n">
         <v>-33811.045</v>
       </c>
+      <c r="HQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8224,6 +8241,7 @@
       <c r="HP14" t="n">
         <v>0</v>
       </c>
+      <c r="HQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8596,6 +8614,7 @@
       <c r="HP15" t="n">
         <v>0</v>
       </c>
+      <c r="HQ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9136,6 +9155,7 @@
       <c r="HP16" t="n">
         <v>908.323</v>
       </c>
+      <c r="HQ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9700,6 +9720,7 @@
       <c r="HP17" t="n">
         <v>35749.511</v>
       </c>
+      <c r="HQ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10240,6 +10261,7 @@
       <c r="HP18" t="n">
         <v>914.875</v>
       </c>
+      <c r="HQ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10924,6 +10946,7 @@
       <c r="HP19" t="n">
         <v>36007.305</v>
       </c>
+      <c r="HQ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11464,6 +11487,7 @@
       <c r="HP20" t="n">
         <v>299.131</v>
       </c>
+      <c r="HQ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12076,6 +12100,7 @@
       <c r="HP21" t="n">
         <v>11773.106</v>
       </c>
+      <c r="HQ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12616,6 +12641,7 @@
       <c r="HP22" t="n">
         <v>10.556</v>
       </c>
+      <c r="HQ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13300,6 +13326,7 @@
       <c r="HP23" t="n">
         <v>415.473</v>
       </c>
+      <c r="HQ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13672,6 +13699,7 @@
       <c r="HP24" t="n">
         <v>0</v>
       </c>
+      <c r="HQ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -14044,6 +14072,7 @@
       <c r="HP25" t="n">
         <v>0</v>
       </c>
+      <c r="HQ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14416,6 +14445,7 @@
       <c r="HP26" t="n">
         <v>0</v>
       </c>
+      <c r="HQ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14788,6 +14818,7 @@
       <c r="HP27" t="n">
         <v>0</v>
       </c>
+      <c r="HQ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15038,6 +15069,7 @@
       <c r="HN28" t="inlineStr"/>
       <c r="HO28" t="inlineStr"/>
       <c r="HP28" t="inlineStr"/>
+      <c r="HQ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15288,6 +15320,7 @@
       <c r="HN29" t="inlineStr"/>
       <c r="HO29" t="inlineStr"/>
       <c r="HP29" t="inlineStr"/>
+      <c r="HQ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15598,6 +15631,7 @@
       <c r="HP30" t="n">
         <v>247.462</v>
       </c>
+      <c r="HQ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15908,6 +15942,7 @@
       <c r="HP31" t="n">
         <v>9739.558000000001</v>
       </c>
+      <c r="HQ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16304,6 +16339,7 @@
       <c r="HP32" t="n">
         <v>6.552</v>
       </c>
+      <c r="HQ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16700,6 +16736,7 @@
       <c r="HP33" t="n">
         <v>257.794</v>
       </c>
+      <c r="HQ33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -2077,7 +2077,9 @@
       <c r="HP2" t="n">
         <v>39.851</v>
       </c>
-      <c r="HQ2" t="inlineStr"/>
+      <c r="HQ2" t="n">
+        <v>44.121</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2762,7 +2764,9 @@
       <c r="HP3" t="n">
         <v>1568.437</v>
       </c>
-      <c r="HQ3" t="inlineStr"/>
+      <c r="HQ3" t="n">
+        <v>1736.484</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3159,7 +3163,9 @@
       <c r="HP4" t="n">
         <v>1.295</v>
       </c>
-      <c r="HQ4" t="inlineStr"/>
+      <c r="HQ4" t="n">
+        <v>1.433</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3556,7 +3562,9 @@
       <c r="HP5" t="n">
         <v>50.95</v>
       </c>
-      <c r="HQ5" t="inlineStr"/>
+      <c r="HQ5" t="n">
+        <v>56.408</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4097,7 +4105,9 @@
       <c r="HP6" t="n">
         <v>660.534</v>
       </c>
-      <c r="HQ6" t="inlineStr"/>
+      <c r="HQ6" t="n">
+        <v>776.203</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4782,7 +4792,9 @@
       <c r="HP7" t="n">
         <v>25997.119</v>
       </c>
-      <c r="HQ7" t="inlineStr"/>
+      <c r="HQ7" t="n">
+        <v>30549.602</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5323,7 +5335,9 @@
       <c r="HP8" t="n">
         <v>736.1369999999999</v>
       </c>
-      <c r="HQ8" t="inlineStr"/>
+      <c r="HQ8" t="n">
+        <v>353.607</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6008,7 +6022,9 @@
       <c r="HP9" t="n">
         <v>28972.726</v>
       </c>
-      <c r="HQ9" t="inlineStr"/>
+      <c r="HQ9" t="n">
+        <v>13917.152</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6325,7 +6341,9 @@
       <c r="HP10" t="n">
         <v>-90.262</v>
       </c>
-      <c r="HQ10" t="inlineStr"/>
+      <c r="HQ10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6642,7 +6660,9 @@
       <c r="HP11" t="n">
         <v>-3552.48</v>
       </c>
-      <c r="HQ11" t="inlineStr"/>
+      <c r="HQ11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7183,7 +7203,9 @@
       <c r="HP12" t="n">
         <v>-859.0700000000001</v>
       </c>
-      <c r="HQ12" t="inlineStr"/>
+      <c r="HQ12" t="n">
+        <v>-234.096</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7868,7 +7890,9 @@
       <c r="HP13" t="n">
         <v>-33811.045</v>
       </c>
-      <c r="HQ13" t="inlineStr"/>
+      <c r="HQ13" t="n">
+        <v>-9213.499</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8241,7 +8265,9 @@
       <c r="HP14" t="n">
         <v>0</v>
       </c>
-      <c r="HQ14" t="inlineStr"/>
+      <c r="HQ14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8614,7 +8640,9 @@
       <c r="HP15" t="n">
         <v>0</v>
       </c>
-      <c r="HQ15" t="inlineStr"/>
+      <c r="HQ15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9155,7 +9183,9 @@
       <c r="HP16" t="n">
         <v>908.323</v>
       </c>
-      <c r="HQ16" t="inlineStr"/>
+      <c r="HQ16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9720,7 +9750,9 @@
       <c r="HP17" t="n">
         <v>35749.511</v>
       </c>
-      <c r="HQ17" t="inlineStr"/>
+      <c r="HQ17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10261,7 +10293,9 @@
       <c r="HP18" t="n">
         <v>914.875</v>
       </c>
-      <c r="HQ18" t="inlineStr"/>
+      <c r="HQ18" t="n">
+        <v>702.246</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10946,7 +10980,9 @@
       <c r="HP19" t="n">
         <v>36007.305</v>
       </c>
-      <c r="HQ19" t="inlineStr"/>
+      <c r="HQ19" t="n">
+        <v>27638.841</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11487,7 +11523,9 @@
       <c r="HP20" t="n">
         <v>299.131</v>
       </c>
-      <c r="HQ20" t="inlineStr"/>
+      <c r="HQ20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12100,7 +12138,9 @@
       <c r="HP21" t="n">
         <v>11773.106</v>
       </c>
-      <c r="HQ21" t="inlineStr"/>
+      <c r="HQ21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12641,7 +12681,9 @@
       <c r="HP22" t="n">
         <v>10.556</v>
       </c>
-      <c r="HQ22" t="inlineStr"/>
+      <c r="HQ22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13326,7 +13368,9 @@
       <c r="HP23" t="n">
         <v>415.473</v>
       </c>
-      <c r="HQ23" t="inlineStr"/>
+      <c r="HQ23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13699,7 +13743,9 @@
       <c r="HP24" t="n">
         <v>0</v>
       </c>
-      <c r="HQ24" t="inlineStr"/>
+      <c r="HQ24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -14072,7 +14118,9 @@
       <c r="HP25" t="n">
         <v>0</v>
       </c>
-      <c r="HQ25" t="inlineStr"/>
+      <c r="HQ25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14445,7 +14493,9 @@
       <c r="HP26" t="n">
         <v>0</v>
       </c>
-      <c r="HQ26" t="inlineStr"/>
+      <c r="HQ26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14818,7 +14868,9 @@
       <c r="HP27" t="n">
         <v>0</v>
       </c>
-      <c r="HQ27" t="inlineStr"/>
+      <c r="HQ27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15069,7 +15121,9 @@
       <c r="HN28" t="inlineStr"/>
       <c r="HO28" t="inlineStr"/>
       <c r="HP28" t="inlineStr"/>
-      <c r="HQ28" t="inlineStr"/>
+      <c r="HQ28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15320,7 +15374,9 @@
       <c r="HN29" t="inlineStr"/>
       <c r="HO29" t="inlineStr"/>
       <c r="HP29" t="inlineStr"/>
-      <c r="HQ29" t="inlineStr"/>
+      <c r="HQ29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15631,7 +15687,9 @@
       <c r="HP30" t="n">
         <v>247.462</v>
       </c>
-      <c r="HQ30" t="inlineStr"/>
+      <c r="HQ30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15942,7 +16000,9 @@
       <c r="HP31" t="n">
         <v>9739.558000000001</v>
       </c>
-      <c r="HQ31" t="inlineStr"/>
+      <c r="HQ31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16339,7 +16399,9 @@
       <c r="HP32" t="n">
         <v>6.552</v>
       </c>
-      <c r="HQ32" t="inlineStr"/>
+      <c r="HQ32" t="n">
+        <v>702.246</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16736,7 +16798,9 @@
       <c r="HP33" t="n">
         <v>257.794</v>
       </c>
-      <c r="HQ33" t="inlineStr"/>
+      <c r="HQ33" t="n">
+        <v>27638.841</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -2078,7 +2078,7 @@
         <v>39.851</v>
       </c>
       <c r="HQ2" t="n">
-        <v>44.121</v>
+        <v>43.738</v>
       </c>
     </row>
     <row r="3">
@@ -2765,7 +2765,7 @@
         <v>1568.437</v>
       </c>
       <c r="HQ3" t="n">
-        <v>1736.484</v>
+        <v>1721.444</v>
       </c>
     </row>
     <row r="4">
@@ -3164,7 +3164,7 @@
         <v>1.295</v>
       </c>
       <c r="HQ4" t="n">
-        <v>1.433</v>
+        <v>1.586</v>
       </c>
     </row>
     <row r="5">
@@ -3563,7 +3563,7 @@
         <v>50.95</v>
       </c>
       <c r="HQ5" t="n">
-        <v>56.408</v>
+        <v>62.405</v>
       </c>
     </row>
     <row r="6">
@@ -4106,7 +4106,7 @@
         <v>660.534</v>
       </c>
       <c r="HQ6" t="n">
-        <v>776.203</v>
+        <v>778.231</v>
       </c>
     </row>
     <row r="7">
@@ -4793,7 +4793,7 @@
         <v>25997.119</v>
       </c>
       <c r="HQ7" t="n">
-        <v>30549.602</v>
+        <v>30629.406</v>
       </c>
     </row>
     <row r="8">
@@ -5336,7 +5336,7 @@
         <v>736.1369999999999</v>
       </c>
       <c r="HQ8" t="n">
-        <v>353.607</v>
+        <v>354.721</v>
       </c>
     </row>
     <row r="9">
@@ -6023,7 +6023,7 @@
         <v>28972.726</v>
       </c>
       <c r="HQ9" t="n">
-        <v>13917.152</v>
+        <v>13961.034</v>
       </c>
     </row>
     <row r="10">
@@ -6342,7 +6342,7 @@
         <v>-90.262</v>
       </c>
       <c r="HQ10" t="n">
-        <v>0</v>
+        <v>-100.447</v>
       </c>
     </row>
     <row r="11">
@@ -6661,7 +6661,7 @@
         <v>-3552.48</v>
       </c>
       <c r="HQ11" t="n">
-        <v>0</v>
+        <v>-3953.368</v>
       </c>
     </row>
     <row r="12">
@@ -7204,7 +7204,7 @@
         <v>-859.0700000000001</v>
       </c>
       <c r="HQ12" t="n">
-        <v>-234.096</v>
+        <v>-136.261</v>
       </c>
     </row>
     <row r="13">
@@ -7891,7 +7891,7 @@
         <v>-33811.045</v>
       </c>
       <c r="HQ13" t="n">
-        <v>-9213.499</v>
+        <v>-5362.923</v>
       </c>
     </row>
     <row r="14">
@@ -9184,7 +9184,7 @@
         <v>908.323</v>
       </c>
       <c r="HQ16" t="n">
-        <v>0</v>
+        <v>709.037</v>
       </c>
     </row>
     <row r="17">
@@ -9751,7 +9751,7 @@
         <v>35749.511</v>
       </c>
       <c r="HQ17" t="n">
-        <v>0</v>
+        <v>27906.098</v>
       </c>
     </row>
     <row r="18">
@@ -10294,7 +10294,7 @@
         <v>914.875</v>
       </c>
       <c r="HQ18" t="n">
-        <v>702.246</v>
+        <v>705.542</v>
       </c>
     </row>
     <row r="19">
@@ -10981,7 +10981,7 @@
         <v>36007.305</v>
       </c>
       <c r="HQ19" t="n">
-        <v>27638.841</v>
+        <v>27768.512</v>
       </c>
     </row>
     <row r="20">
@@ -11524,7 +11524,7 @@
         <v>299.131</v>
       </c>
       <c r="HQ20" t="n">
-        <v>0</v>
+        <v>149.01</v>
       </c>
     </row>
     <row r="21">
@@ -12139,7 +12139,7 @@
         <v>11773.106</v>
       </c>
       <c r="HQ21" t="n">
-        <v>0</v>
+        <v>5864.685</v>
       </c>
     </row>
     <row r="22">
@@ -12682,7 +12682,7 @@
         <v>10.556</v>
       </c>
       <c r="HQ22" t="n">
-        <v>0</v>
+        <v>12.982</v>
       </c>
     </row>
     <row r="23">
@@ -13369,7 +13369,7 @@
         <v>415.473</v>
       </c>
       <c r="HQ23" t="n">
-        <v>0</v>
+        <v>510.933</v>
       </c>
     </row>
     <row r="24">
@@ -15121,9 +15121,7 @@
       <c r="HN28" t="inlineStr"/>
       <c r="HO28" t="inlineStr"/>
       <c r="HP28" t="inlineStr"/>
-      <c r="HQ28" t="n">
-        <v>0</v>
-      </c>
+      <c r="HQ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15374,9 +15372,7 @@
       <c r="HN29" t="inlineStr"/>
       <c r="HO29" t="inlineStr"/>
       <c r="HP29" t="inlineStr"/>
-      <c r="HQ29" t="n">
-        <v>0</v>
-      </c>
+      <c r="HQ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15688,7 +15684,7 @@
         <v>247.462</v>
       </c>
       <c r="HQ30" t="n">
-        <v>0</v>
+        <v>190.289</v>
       </c>
     </row>
     <row r="31">
@@ -16001,7 +15997,7 @@
         <v>9739.558000000001</v>
       </c>
       <c r="HQ31" t="n">
-        <v>0</v>
+        <v>7489.347</v>
       </c>
     </row>
     <row r="32">
@@ -16400,7 +16396,7 @@
         <v>6.552</v>
       </c>
       <c r="HQ32" t="n">
-        <v>702.246</v>
+        <v>-3.495</v>
       </c>
     </row>
     <row r="33">
@@ -16799,7 +16795,7 @@
         <v>257.794</v>
       </c>
       <c r="HQ33" t="n">
-        <v>27638.841</v>
+        <v>-137.586</v>
       </c>
     </row>
   </sheetData>

--- a/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
+++ b/services/data_raw/eurostat/AT_gas_NRG_CB_GASM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HQ33"/>
+  <dimension ref="A1:HT33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,6 +1535,21 @@
       <c r="HQ1" t="inlineStr">
         <is>
           <t>2026-03</t>
+        </is>
+      </c>
+      <c r="HR1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="HS1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="HT1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2080,6 +2095,15 @@
       <c r="HQ2" t="n">
         <v>43.738</v>
       </c>
+      <c r="HR2" t="n">
+        <v>28.799</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>40.833</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>44.442</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2766,6 +2790,15 @@
       </c>
       <c r="HQ3" t="n">
         <v>1721.444</v>
+      </c>
+      <c r="HR3" t="n">
+        <v>1133.453</v>
+      </c>
+      <c r="HS3" t="n">
+        <v>1607.108</v>
+      </c>
+      <c r="HT3" t="n">
+        <v>1749.143</v>
       </c>
     </row>
     <row r="4">
@@ -3166,6 +3199,15 @@
       <c r="HQ4" t="n">
         <v>1.586</v>
       </c>
+      <c r="HR4" t="n">
+        <v>1.402</v>
+      </c>
+      <c r="HS4" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="HT4" t="n">
+        <v>1.563</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3565,6 +3607,15 @@
       <c r="HQ5" t="n">
         <v>62.405</v>
       </c>
+      <c r="HR5" t="n">
+        <v>55.194</v>
+      </c>
+      <c r="HS5" t="n">
+        <v>67.255</v>
+      </c>
+      <c r="HT5" t="n">
+        <v>61.528</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4108,6 +4159,15 @@
       <c r="HQ6" t="n">
         <v>778.231</v>
       </c>
+      <c r="HR6" t="n">
+        <v>1284.156</v>
+      </c>
+      <c r="HS6" t="n">
+        <v>1358.595</v>
+      </c>
+      <c r="HT6" t="n">
+        <v>1339.911</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4794,6 +4854,15 @@
       </c>
       <c r="HQ7" t="n">
         <v>30629.406</v>
+      </c>
+      <c r="HR7" t="n">
+        <v>50541.448</v>
+      </c>
+      <c r="HS7" t="n">
+        <v>53471.182</v>
+      </c>
+      <c r="HT7" t="n">
+        <v>52735.855</v>
       </c>
     </row>
     <row r="8">
@@ -5338,6 +5407,15 @@
       <c r="HQ8" t="n">
         <v>354.721</v>
       </c>
+      <c r="HR8" t="n">
+        <v>392.08</v>
+      </c>
+      <c r="HS8" t="n">
+        <v>322.238</v>
+      </c>
+      <c r="HT8" t="n">
+        <v>383.476</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6024,6 +6102,15 @@
       </c>
       <c r="HQ9" t="n">
         <v>13961.034</v>
+      </c>
+      <c r="HR9" t="n">
+        <v>15431.395</v>
+      </c>
+      <c r="HS9" t="n">
+        <v>12682.608</v>
+      </c>
+      <c r="HT9" t="n">
+        <v>15092.765</v>
       </c>
     </row>
     <row r="10">
@@ -6344,6 +6431,15 @@
       <c r="HQ10" t="n">
         <v>-100.447</v>
       </c>
+      <c r="HR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS10" t="n">
+        <v>-12.994</v>
+      </c>
+      <c r="HT10" t="n">
+        <v>-14.63</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6663,6 +6759,15 @@
       <c r="HQ11" t="n">
         <v>-3953.368</v>
       </c>
+      <c r="HR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS11" t="n">
+        <v>-511.604</v>
+      </c>
+      <c r="HT11" t="n">
+        <v>-575.5599999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7206,6 +7311,15 @@
       <c r="HQ12" t="n">
         <v>-136.261</v>
       </c>
+      <c r="HR12" t="n">
+        <v>369.075</v>
+      </c>
+      <c r="HS12" t="n">
+        <v>708.679</v>
+      </c>
+      <c r="HT12" t="n">
+        <v>712.355</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7892,6 +8006,15 @@
       </c>
       <c r="HQ13" t="n">
         <v>-5362.923</v>
+      </c>
+      <c r="HR13" t="n">
+        <v>14525.957</v>
+      </c>
+      <c r="HS13" t="n">
+        <v>27891.996</v>
+      </c>
+      <c r="HT13" t="n">
+        <v>28036.67</v>
       </c>
     </row>
     <row r="14">
@@ -8268,6 +8391,15 @@
       <c r="HQ14" t="n">
         <v>0</v>
       </c>
+      <c r="HR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8643,6 +8775,15 @@
       <c r="HQ15" t="n">
         <v>0</v>
       </c>
+      <c r="HR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9186,6 +9327,15 @@
       <c r="HQ16" t="n">
         <v>709.037</v>
       </c>
+      <c r="HR16" t="n">
+        <v>557.591</v>
+      </c>
+      <c r="HS16" t="n">
+        <v>377.898</v>
+      </c>
+      <c r="HT16" t="n">
+        <v>299.353</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9752,6 +9902,15 @@
       </c>
       <c r="HQ17" t="n">
         <v>27906.098</v>
+      </c>
+      <c r="HR17" t="n">
+        <v>21945.516</v>
+      </c>
+      <c r="HS17" t="n">
+        <v>14873.2</v>
+      </c>
+      <c r="HT17" t="n">
+        <v>11781.838</v>
       </c>
     </row>
     <row r="18">
@@ -10296,6 +10455,15 @@
       <c r="HQ18" t="n">
         <v>705.542</v>
       </c>
+      <c r="HR18" t="n">
+        <v>553.202</v>
+      </c>
+      <c r="HS18" t="n">
+        <v>383.214</v>
+      </c>
+      <c r="HT18" t="n">
+        <v>304.715</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10982,6 +11150,15 @@
       </c>
       <c r="HQ19" t="n">
         <v>27768.512</v>
+      </c>
+      <c r="HR19" t="n">
+        <v>21772.743</v>
+      </c>
+      <c r="HS19" t="n">
+        <v>15082.545</v>
+      </c>
+      <c r="HT19" t="n">
+        <v>11992.651</v>
       </c>
     </row>
     <row r="20">
@@ -11526,6 +11703,15 @@
       <c r="HQ20" t="n">
         <v>149.01</v>
       </c>
+      <c r="HR20" t="n">
+        <v>104.508</v>
+      </c>
+      <c r="HS20" t="n">
+        <v>14.291</v>
+      </c>
+      <c r="HT20" t="n">
+        <v>12.244</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12140,6 +12326,15 @@
       </c>
       <c r="HQ21" t="n">
         <v>5864.685</v>
+      </c>
+      <c r="HR21" t="n">
+        <v>4113.197</v>
+      </c>
+      <c r="HS21" t="n">
+        <v>562.452</v>
+      </c>
+      <c r="HT21" t="n">
+        <v>481.914</v>
       </c>
     </row>
     <row r="22">
@@ -12684,6 +12879,15 @@
       <c r="HQ22" t="n">
         <v>12.982</v>
       </c>
+      <c r="HR22" t="n">
+        <v>13.352</v>
+      </c>
+      <c r="HS22" t="n">
+        <v>17.827</v>
+      </c>
+      <c r="HT22" t="n">
+        <v>15.878</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13370,6 +13574,15 @@
       </c>
       <c r="HQ23" t="n">
         <v>510.933</v>
+      </c>
+      <c r="HR23" t="n">
+        <v>525.5069999999999</v>
+      </c>
+      <c r="HS23" t="n">
+        <v>701.646</v>
+      </c>
+      <c r="HT23" t="n">
+        <v>624.912</v>
       </c>
     </row>
     <row r="24">
@@ -13746,6 +13959,15 @@
       <c r="HQ24" t="n">
         <v>0</v>
       </c>
+      <c r="HR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -14121,6 +14343,15 @@
       <c r="HQ25" t="n">
         <v>0</v>
       </c>
+      <c r="HR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14496,6 +14727,15 @@
       <c r="HQ26" t="n">
         <v>0</v>
       </c>
+      <c r="HR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14869,6 +15109,15 @@
         <v>0</v>
       </c>
       <c r="HQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15122,6 +15371,9 @@
       <c r="HO28" t="inlineStr"/>
       <c r="HP28" t="inlineStr"/>
       <c r="HQ28" t="inlineStr"/>
+      <c r="HR28" t="inlineStr"/>
+      <c r="HS28" t="inlineStr"/>
+      <c r="HT28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15373,6 +15625,9 @@
       <c r="HO29" t="inlineStr"/>
       <c r="HP29" t="inlineStr"/>
       <c r="HQ29" t="inlineStr"/>
+      <c r="HR29" t="inlineStr"/>
+      <c r="HS29" t="inlineStr"/>
+      <c r="HT29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15686,6 +15941,15 @@
       <c r="HQ30" t="n">
         <v>190.289</v>
       </c>
+      <c r="HR30" t="n">
+        <v>130.942</v>
+      </c>
+      <c r="HS30" t="n">
+        <v>72.247</v>
+      </c>
+      <c r="HT30" t="n">
+        <v>45.767</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15999,6 +16263,15 @@
       <c r="HQ31" t="n">
         <v>7489.347</v>
       </c>
+      <c r="HR31" t="n">
+        <v>5153.576</v>
+      </c>
+      <c r="HS31" t="n">
+        <v>2843.46</v>
+      </c>
+      <c r="HT31" t="n">
+        <v>1801.27</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16398,6 +16671,15 @@
       <c r="HQ32" t="n">
         <v>-3.495</v>
       </c>
+      <c r="HR32" t="n">
+        <v>-4.389</v>
+      </c>
+      <c r="HS32" t="n">
+        <v>5.316</v>
+      </c>
+      <c r="HT32" t="n">
+        <v>5.362</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -16797,6 +17079,15 @@
       <c r="HQ33" t="n">
         <v>-137.586</v>
       </c>
+      <c r="HR33" t="n">
+        <v>-172.773</v>
+      </c>
+      <c r="HS33" t="n">
+        <v>209.345</v>
+      </c>
+      <c r="HT33" t="n">
+        <v>210.813</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
